--- a/prep_environment/Environmental_data_metadata.xlsx
+++ b/prep_environment/Environmental_data_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hillna\OneDrive - University of Tasmania\UTAS_work\Projects\Benthic Diversity ARC\Analysis\ARC_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjansen\Desktop\science\SouthernOceanBiodiversityMapping\ARC_Data\prep_environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823D4762-5F5B-452F-8073-FE7416B561C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843B5D3B-4803-4B57-9464-6E96E946F316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{37A04AC2-0244-4B87-B563-6F6FD289412D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{37A04AC2-0244-4B87-B563-6F6FD289412D}"/>
   </bookViews>
   <sheets>
     <sheet name="BioMAS environmental Metadata" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="148">
   <si>
     <t>Variable</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Reprojected?</t>
   </si>
   <si>
-    <t>gebco bathy</t>
-  </si>
-  <si>
     <t>Usage Notes</t>
   </si>
   <si>
@@ -283,9 +280,6 @@
     <t>Max sea ice cover during summer (Dec- Feb) 2002-2020</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t>geomorph</t>
   </si>
   <si>
@@ -470,6 +464,21 @@
   </si>
   <si>
     <t>issues with VM extraction raadtools- NIc</t>
+  </si>
+  <si>
+    <t>gebco bathymetry (2021)</t>
+  </si>
+  <si>
+    <t>WAOM</t>
+  </si>
+  <si>
+    <t>2km</t>
+  </si>
+  <si>
+    <t>GEBCO</t>
+  </si>
+  <si>
+    <t>Slope</t>
   </si>
 </sst>
 </file>
@@ -902,21 +911,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7C515A-C8AD-4B88-B018-D4662A000C62}">
   <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="58.7109375" customWidth="1"/>
-    <col min="4" max="4" width="54.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" customWidth="1"/>
-    <col min="8" max="8" width="47.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="30.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="58.6640625" customWidth="1"/>
+    <col min="4" max="4" width="54.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" customWidth="1"/>
+    <col min="8" max="8" width="47.33203125" customWidth="1"/>
+    <col min="9" max="9" width="24.5546875" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -945,55 +954,82 @@
         <v>2</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
+      <c r="F2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" t="s">
+        <v>138</v>
+      </c>
       <c r="J2" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
+      </c>
+      <c r="F3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" t="s">
+        <v>138</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" t="s">
+        <v>138</v>
+      </c>
       <c r="J4" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1001,16 +1037,25 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
+      <c r="F5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" t="s">
+        <v>138</v>
+      </c>
       <c r="J5" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1018,16 +1063,25 @@
         <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
+      <c r="F6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" t="s">
+        <v>138</v>
+      </c>
       <c r="J6" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -1035,44 +1089,65 @@
         <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
+      <c r="H7" t="s">
+        <v>138</v>
+      </c>
       <c r="J7" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
+      <c r="F8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8" t="s">
+        <v>137</v>
+      </c>
       <c r="J8" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
       </c>
+      <c r="F9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H9" t="s">
+        <v>137</v>
+      </c>
       <c r="J9" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1080,13 +1155,16 @@
         <v>25</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
+      </c>
+      <c r="H10" t="s">
+        <v>138</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -1094,13 +1172,16 @@
         <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
+      </c>
+      <c r="H11" t="s">
+        <v>138</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -1108,572 +1189,575 @@
         <v>27</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
+      </c>
+      <c r="H12" t="s">
+        <v>138</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
         <v>52</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>53</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F19" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" t="s">
+        <v>137</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" t="s">
+        <v>137</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" t="s">
-        <v>140</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" t="s">
-        <v>140</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" t="s">
-        <v>140</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" t="s">
-        <v>140</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="E24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" t="s">
+        <v>119</v>
+      </c>
+      <c r="H24" t="s">
+        <v>137</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H25" t="s">
+        <v>137</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" t="s">
-        <v>143</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" t="s">
+        <v>135</v>
+      </c>
+      <c r="G26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" t="s">
         <v>137</v>
       </c>
-      <c r="G19" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" t="s">
-        <v>139</v>
-      </c>
-      <c r="J19" s="6" t="s">
+      <c r="J26" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>138</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="H27" t="s">
         <v>137</v>
       </c>
-      <c r="G20" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" t="s">
-        <v>139</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="J27" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" t="s">
+        <v>135</v>
+      </c>
+      <c r="G28" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" t="s">
         <v>137</v>
       </c>
-      <c r="G21" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" t="s">
-        <v>139</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" t="s">
-        <v>138</v>
-      </c>
-      <c r="F22" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" t="s">
-        <v>121</v>
-      </c>
-      <c r="H22" t="s">
-        <v>139</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>138</v>
-      </c>
-      <c r="F23" t="s">
-        <v>137</v>
-      </c>
-      <c r="G23" t="s">
-        <v>121</v>
-      </c>
-      <c r="H23" t="s">
-        <v>139</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" t="s">
-        <v>137</v>
-      </c>
-      <c r="G24" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G25" t="s">
-        <v>121</v>
-      </c>
-      <c r="H25" t="s">
-        <v>139</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F26" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" t="s">
-        <v>121</v>
-      </c>
-      <c r="H26" t="s">
-        <v>139</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" t="s">
-        <v>138</v>
-      </c>
-      <c r="F27" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" t="s">
-        <v>121</v>
-      </c>
-      <c r="H27" t="s">
-        <v>139</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
-        <v>138</v>
-      </c>
-      <c r="F28" t="s">
-        <v>137</v>
-      </c>
-      <c r="G28" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" t="s">
-        <v>139</v>
-      </c>
       <c r="J28" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" t="s">
-        <v>85</v>
-      </c>
-      <c r="H31" t="s">
-        <v>86</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>31</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>32</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1688,16 +1772,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1504AF42-C50A-43AE-A28F-E1ED9575DCB0}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="42.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>

--- a/prep_environment/Environmental_data_metadata.xlsx
+++ b/prep_environment/Environmental_data_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hillna\OneDrive - University of Tasmania\UTAS_work\Projects\Benthic Diversity ARC\Analysis\ARC_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitytasmania-my.sharepoint.com/personal/nicole_hill_utas_edu_au/Documents/UTAS_work/Projects/Benthic Diversity ARC/Analysis/ARC_Data/prep_environment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823D4762-5F5B-452F-8073-FE7416B561C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="13_ncr:1_{823D4762-5F5B-452F-8073-FE7416B561C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{683C39E7-8ED8-4762-B6DB-5E1BE41D46DB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{37A04AC2-0244-4B87-B563-6F6FD289412D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21600" xr2:uid="{37A04AC2-0244-4B87-B563-6F6FD289412D}"/>
   </bookViews>
   <sheets>
     <sheet name="BioMAS environmental Metadata" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="227">
   <si>
     <t>Variable</t>
   </si>
@@ -127,15 +127,6 @@
     <t>Bottom salinity (Woam2k?)</t>
   </si>
   <si>
-    <t>C/N/O2- B-SOSE</t>
-  </si>
-  <si>
-    <t>C/N/O2- WOMBAT?</t>
-  </si>
-  <si>
-    <t>FAM- to come!</t>
-  </si>
-  <si>
     <t>Abbreviation</t>
   </si>
   <si>
@@ -169,9 +160,6 @@
     <t>Good to go!</t>
   </si>
   <si>
-    <t>distance to shelf break</t>
-  </si>
-  <si>
     <t>to get once have ROMS upgrade- Jan</t>
   </si>
   <si>
@@ -184,12 +172,6 @@
     <t>geomorphology</t>
   </si>
   <si>
-    <t>Chase down which model would be best for region  and see!</t>
-  </si>
-  <si>
-    <t>Almost there!- Jan</t>
-  </si>
-  <si>
     <t>OISST via raadtools</t>
   </si>
   <si>
@@ -253,15 +235,6 @@
     <t>Standard deviation of summer (Dec-Feb) SST (2002-2020)</t>
   </si>
   <si>
-    <t>Most recent version from AP- need to wrangle-Nic</t>
-  </si>
-  <si>
-    <t>N/P/Si Bioracle??</t>
-  </si>
-  <si>
-    <t>O2/Si/P (CARS 2009)</t>
-  </si>
-  <si>
     <t>Standard deviation in sea ice cover during summer (Dec- Feb) 2002-2020</t>
   </si>
   <si>
@@ -283,9 +256,6 @@
     <t>Max sea ice cover during summer (Dec- Feb) 2002-2020</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t>geomorph</t>
   </si>
   <si>
@@ -469,7 +439,283 @@
     <t>0-1</t>
   </si>
   <si>
-    <t>issues with VM extraction raadtools- NIc</t>
+    <t>issues with VM extraction raadtools- sorted- but no real variation on the shelf. Not used.</t>
+  </si>
+  <si>
+    <t>B-SOSE (BGC  Southern Ocean State Estimate)</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_bot_arag_BSOSE["arag_mean"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_bot_arag_BSOSE["arag_sd"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_bot_NO3_BSOSE["no3_mean"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_bot_NO3_BSOSE["no3_sd"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_bot_O2_BSOSE["o2_mean"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_bot_O2_BSOSE["o2_sd"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_bot_PO4_BSOSE["po4_mean"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_bot_PO4_BSOSE["po4_sd"]</t>
+  </si>
+  <si>
+    <t>O/mol</t>
+  </si>
+  <si>
+    <t>P/mol</t>
+  </si>
+  <si>
+    <t>N/mol</t>
+  </si>
+  <si>
+    <t>http://sose.ucsd.edu/</t>
+  </si>
+  <si>
+    <t>0.16667deg lon; 1/6 degree lat * cos(lat)</t>
+  </si>
+  <si>
+    <t>BSOSE aragonite sd</t>
+  </si>
+  <si>
+    <t>BSOSE nitrate mean</t>
+  </si>
+  <si>
+    <t>BSOSE nitrate sd</t>
+  </si>
+  <si>
+    <t>BSOSE posphate mean</t>
+  </si>
+  <si>
+    <t>BSOSE phosphate sd</t>
+  </si>
+  <si>
+    <t>BSOSE oxygen mean</t>
+  </si>
+  <si>
+    <t>BSOSE oxygen sd</t>
+  </si>
+  <si>
+    <t>arag_mean</t>
+  </si>
+  <si>
+    <t>arag_sd</t>
+  </si>
+  <si>
+    <t>no3_mean</t>
+  </si>
+  <si>
+    <t>no3_sd</t>
+  </si>
+  <si>
+    <t>o2_mean</t>
+  </si>
+  <si>
+    <t>o2_sd</t>
+  </si>
+  <si>
+    <t>po4_mean</t>
+  </si>
+  <si>
+    <t>po4_sd</t>
+  </si>
+  <si>
+    <t>BSOSE  aragonite mean</t>
+  </si>
+  <si>
+    <t>Mean seafloor aragonite concentration 2013-2019</t>
+  </si>
+  <si>
+    <t>Standard deviation seafloor aragonite concentration 2013-2019</t>
+  </si>
+  <si>
+    <t>Mean seafloor NO3 concentration 2013-2019</t>
+  </si>
+  <si>
+    <t>Standard seafloor deviation NO3 concentration 2013-2019</t>
+  </si>
+  <si>
+    <t>Mean seafloor O2 concentration 2013-2019</t>
+  </si>
+  <si>
+    <t>Standard deviation seafloor O2 concentration 2013-2019</t>
+  </si>
+  <si>
+    <t>Mean seafloor PO4 concentration 2013-2019</t>
+  </si>
+  <si>
+    <t>Standard deviation seafloor PO4 concentration 2013-2019</t>
+  </si>
+  <si>
+    <t>CARS nitrate sd</t>
+  </si>
+  <si>
+    <t>CARS oxygen mean</t>
+  </si>
+  <si>
+    <t>CARS oxygen sd</t>
+  </si>
+  <si>
+    <t>CARS posphate mean</t>
+  </si>
+  <si>
+    <t>CARS phosphate sd</t>
+  </si>
+  <si>
+    <t>CARS nitrate mean</t>
+  </si>
+  <si>
+    <t>http://www.marine.csiro.au/~dunn/cars2009/</t>
+  </si>
+  <si>
+    <t>0.5 deg</t>
+  </si>
+  <si>
+    <t>umol/l</t>
+  </si>
+  <si>
+    <t>ml/l</t>
+  </si>
+  <si>
+    <t>Geoscience Australia</t>
+  </si>
+  <si>
+    <t>Good to go! But model not constrained by observations in ROI</t>
+  </si>
+  <si>
+    <t>Good to go! But not many observations in ROI</t>
+  </si>
+  <si>
+    <t>CARS 2009 (CSIRO Atlas of Regional Seas)</t>
+  </si>
+  <si>
+    <t>CARS oxygen seasonal range</t>
+  </si>
+  <si>
+    <t>CARS nitrate seasonal range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean seafloor NO3 concentration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard seafloor deviation NO3 concentration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean seafloor O2 concentration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard deviation seafloor O2 concentration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean seafloor PO4 concentration </t>
+  </si>
+  <si>
+    <t>CARS posphate seasonal range</t>
+  </si>
+  <si>
+    <t>Seasonal range seafloor O2 concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal range seafloor PO4 concentration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal Rangeseafloor NO3 concentration </t>
+  </si>
+  <si>
+    <t>Not yet calculated- will do if likely to be useful based on distribution of samples</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_NO3["mean"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_NO3["seas_range"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_NO3["std_dev"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_O2["mean"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_O2["seas_range"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_O2["std_dev"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_PO4["mean"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_PO4["seas_range"]</t>
+  </si>
+  <si>
+    <t>Circumpolar_EnvData_500m_shelf_CARS_PO4["std_dev"]</t>
+  </si>
+  <si>
+    <t>Generated by</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Extraction/formatting code</t>
+  </si>
+  <si>
+    <t>Nicole</t>
+  </si>
+  <si>
+    <t>Slope</t>
+  </si>
+  <si>
+    <t>ARC_Data/prep_environment/1b_Satellite_SST_SSH_Ice.R</t>
+  </si>
+  <si>
+    <t>ARC_Data/prep_environment/1c_BGC.R</t>
+  </si>
+  <si>
+    <t>ARC_Data/prep_environment/1a_Bathymetry_NPP_ROMS.R</t>
+  </si>
+  <si>
+    <t>https://www.ncei.noaa.gov/products/optimum-interpolation-sst</t>
+  </si>
+  <si>
+    <t>https://nsidc.org/data/amsre</t>
+  </si>
+  <si>
+    <t>CARS_NO3_mean</t>
+  </si>
+  <si>
+    <t>CARS_NO3_seas_range</t>
+  </si>
+  <si>
+    <t>CARS_NO3_std_dev</t>
+  </si>
+  <si>
+    <t>CARS_O2_mean</t>
+  </si>
+  <si>
+    <t>CARS_O2_seas_range</t>
+  </si>
+  <si>
+    <t>CARS_O2_std_dev</t>
+  </si>
+  <si>
+    <t>CARS_PO4_mean</t>
+  </si>
+  <si>
+    <t>CARS_PO4_seas_range</t>
+  </si>
+  <si>
+    <t>CARS_PO4_std_dev</t>
   </si>
 </sst>
 </file>
@@ -535,12 +781,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -571,7 +823,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -581,11 +833,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -901,27 +1164,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7C515A-C8AD-4B88-B018-D4662A000C62}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="58.7109375" customWidth="1"/>
-    <col min="4" max="4" width="54.140625" customWidth="1"/>
+    <col min="4" max="4" width="65.42578125" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" customWidth="1"/>
     <col min="7" max="7" width="21.5703125" customWidth="1"/>
-    <col min="8" max="8" width="47.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="55.28515625" customWidth="1"/>
+    <col min="9" max="9" width="43.42578125" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" customWidth="1"/>
+    <col min="11" max="11" width="41.42578125" customWidth="1"/>
+    <col min="12" max="12" width="60" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
@@ -944,56 +1209,80 @@
       <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>209</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="J3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>209</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1001,16 +1290,22 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" t="s">
+        <v>209</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1018,16 +1313,22 @@
         <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>209</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -1035,650 +1336,1460 @@
         <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J7" t="s">
+        <v>209</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>209</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" t="s">
+        <v>209</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" t="s">
+        <v>209</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" t="s">
+        <v>209</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" t="s">
+        <v>209</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="B13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="B24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" t="s">
-        <v>140</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" t="s">
-        <v>140</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" t="s">
-        <v>140</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" t="s">
-        <v>140</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" t="s">
-        <v>143</v>
-      </c>
-      <c r="F19" t="s">
-        <v>137</v>
-      </c>
-      <c r="G19" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" t="s">
-        <v>139</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>138</v>
-      </c>
-      <c r="F20" t="s">
-        <v>137</v>
-      </c>
-      <c r="G20" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" t="s">
-        <v>139</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F21" t="s">
-        <v>137</v>
-      </c>
-      <c r="G21" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" t="s">
-        <v>139</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" t="s">
-        <v>138</v>
-      </c>
-      <c r="F22" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" t="s">
-        <v>121</v>
-      </c>
-      <c r="H22" t="s">
-        <v>139</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>138</v>
-      </c>
-      <c r="F23" t="s">
-        <v>137</v>
-      </c>
-      <c r="G23" t="s">
-        <v>121</v>
-      </c>
-      <c r="H23" t="s">
-        <v>139</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" t="s">
-        <v>137</v>
-      </c>
-      <c r="G24" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G25" t="s">
-        <v>121</v>
-      </c>
-      <c r="H25" t="s">
-        <v>139</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="7" t="s">
+      <c r="L47" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" t="s">
+        <v>75</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F26" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" t="s">
-        <v>121</v>
-      </c>
-      <c r="H26" t="s">
-        <v>139</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" t="s">
-        <v>138</v>
-      </c>
-      <c r="F27" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" t="s">
-        <v>121</v>
-      </c>
-      <c r="H27" t="s">
-        <v>139</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
-        <v>138</v>
-      </c>
-      <c r="F28" t="s">
-        <v>137</v>
-      </c>
-      <c r="G28" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" t="s">
-        <v>139</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J30" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" t="s">
-        <v>85</v>
-      </c>
-      <c r="H31" t="s">
-        <v>86</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>50</v>
-      </c>
+      <c r="L49" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I31" r:id="rId1" xr:uid="{48012E50-483A-45A3-8AFC-F0E5B49421FE}"/>
+    <hyperlink ref="I46" r:id="rId1" xr:uid="{48012E50-483A-45A3-8AFC-F0E5B49421FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -1699,19 +2810,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>

--- a/prep_environment/Environmental_data_metadata.xlsx
+++ b/prep_environment/Environmental_data_metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hillna\OneDrive - University of Tasmania\UTAS_work\Projects\Benthic Diversity ARC\Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitytasmania-my.sharepoint.com/personal/nicole_hill_utas_edu_au/Documents/UTAS_work/Projects/Benthic Diversity ARC/Analysis/ARC_Data/prep_environment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B83415-F269-450B-A5A1-C938D9D9F20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{84B83415-F269-450B-A5A1-C938D9D9F20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABF1C5A4-DF58-4A90-84C0-238A2FF3799A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{37A04AC2-0244-4B87-B563-6F6FD289412D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{37A04AC2-0244-4B87-B563-6F6FD289412D}"/>
   </bookViews>
   <sheets>
     <sheet name="BioMAS environmental Metadata" sheetId="1" r:id="rId1"/>
@@ -844,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -878,6 +878,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2247,79 +2251,79 @@
         <v>183</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="J31" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K31" s="7" t="s">
+      <c r="J31" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="K31" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="L31" s="8" t="s">
+      <c r="L31" s="17" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+    <row r="32" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="J32" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K32" s="7" t="s">
+      <c r="J32" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="K32" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="L32" s="8" t="s">
+      <c r="L32" s="17" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2589,117 +2593,117 @@
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
+    <row r="40" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="H40" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="J40" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="K40" s="15" t="s">
+      <c r="J40" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K40" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="L40" s="17" t="s">
+      <c r="L40" s="14" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
+    <row r="41" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="F41" s="15" t="s">
+      <c r="F41" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="G41" s="15" t="s">
+      <c r="G41" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="H41" s="15" t="s">
+      <c r="H41" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="J41" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="K41" s="15" t="s">
+      <c r="J41" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K41" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="L41" s="17" t="s">
+      <c r="L41" s="14" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
+    <row r="42" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="G42" s="15" t="s">
+      <c r="G42" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H42" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="I42" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="J42" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="K42" s="15" t="s">
+      <c r="J42" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K42" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="L42" s="17" t="s">
+      <c r="L42" s="14" t="s">
         <v>184</v>
       </c>
     </row>
